--- a/Docs/PiG Arcelor 2018.xlsx
+++ b/Docs/PiG Arcelor 2018.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -68,6 +68,48 @@
   </si>
   <si>
     <t>PiG</t>
+  </si>
+  <si>
+    <t>Prod:</t>
+  </si>
+  <si>
+    <t>Self:</t>
+  </si>
+  <si>
+    <t>Aquí:</t>
+  </si>
+  <si>
+    <t>Dif:</t>
+  </si>
+  <si>
+    <t>Deutschland</t>
+  </si>
+  <si>
+    <t>Biotechnology C USD Acc</t>
+  </si>
+  <si>
+    <t>DWS Aktien Strategie Deutschland</t>
+  </si>
+  <si>
+    <t>NB Capital Plus FI</t>
+  </si>
+  <si>
+    <t>Global Technology A-Acc-EUR</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Total parts compres reals:</t>
+  </si>
+  <si>
+    <t>Total parts vendes reals:</t>
+  </si>
+  <si>
+    <t>Total parts en cartera:</t>
+  </si>
+  <si>
+    <t>Total parts:</t>
   </si>
 </sst>
 </file>
@@ -77,8 +119,8 @@
   <numFmts count="4">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000\ &quot;€&quot;;[Red]\-#,##0.0000\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000\ &quot;€&quot;;[Red]\-#,##0.0000\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -149,8 +191,8 @@
     <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,12 +487,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5.7265625" style="14" customWidth="1"/>
     <col min="2" max="2" width="13.7265625" customWidth="1"/>
     <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="10.81640625" customWidth="1"/>
     <col min="8" max="8" width="11.6328125" style="13" customWidth="1"/>
@@ -706,6 +750,162 @@
         <v>-2.1079999998619314E-2</v>
       </c>
     </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="6">
+        <v>777.35</v>
+      </c>
+      <c r="D17" s="6">
+        <v>777.35699999999997</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="6">
+        <v>6132.72</v>
+      </c>
+      <c r="D18" s="6">
+        <v>6511.21</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-378.49</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="6">
+        <v>17922.04</v>
+      </c>
+      <c r="D19" s="6">
+        <v>17928.550999999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-6.5110000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1588.63</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1583.24</v>
+      </c>
+      <c r="E20" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="6">
+        <v>27338.26</v>
+      </c>
+      <c r="D21" s="6">
+        <v>27337.143</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.117</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>26084.35</v>
+      </c>
+      <c r="D22" s="6">
+        <v>26084.298999999999</v>
+      </c>
+      <c r="E22" s="6">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="6">
+        <v>79843.350000000006</v>
+      </c>
+      <c r="D23" s="6">
+        <v>80221.8</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-378.45</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26">
+        <v>64911.250999999997</v>
+      </c>
+      <c r="D26">
+        <f>C26</f>
+        <v>64911.250999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27">
+        <v>56026.048000000003</v>
+      </c>
+      <c r="D27">
+        <f>+D26-C27</f>
+        <v>8885.2029999999941</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28">
+        <v>3787.0189999999998</v>
+      </c>
+      <c r="D28">
+        <f>+D27-C28</f>
+        <v>5098.1839999999938</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29">
+        <v>5098.1840000000002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Docs/PiG Arcelor 2018.xlsx
+++ b/Docs/PiG Arcelor 2018.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -122,7 +122,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000\ &quot;€&quot;;[Red]\-#,##0.0000\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,13 +138,49 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -156,10 +192,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -193,8 +232,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -487,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5.7265625" style="14" customWidth="1"/>
@@ -906,6 +961,153 @@
         <v>5098.1840000000002</v>
       </c>
     </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="4">
+        <v>166</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="5">
+        <v>43389</v>
+      </c>
+      <c r="D33" s="8">
+        <v>1600</v>
+      </c>
+      <c r="E33" s="17">
+        <f>D33</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="4">
+        <v>169</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="5">
+        <v>43458</v>
+      </c>
+      <c r="D34" s="4">
+        <v>648</v>
+      </c>
+      <c r="E34" s="17">
+        <f>E33-D34</f>
+        <v>952</v>
+      </c>
+      <c r="F34" s="19">
+        <f>D34</f>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="4">
+        <v>174</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="5">
+        <v>43550</v>
+      </c>
+      <c r="D35" s="4">
+        <v>700</v>
+      </c>
+      <c r="E35" s="17">
+        <f>E34+D35</f>
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="4">
+        <v>177</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="5">
+        <v>43797</v>
+      </c>
+      <c r="D36" s="8">
+        <v>1252</v>
+      </c>
+      <c r="E36" s="17">
+        <f>E35-D36</f>
+        <v>400</v>
+      </c>
+      <c r="F36" s="19">
+        <f>D33-F34</f>
+        <v>952</v>
+      </c>
+      <c r="G36" s="21">
+        <f>D36-F36</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="4">
+        <v>178</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="5">
+        <v>43802</v>
+      </c>
+      <c r="D37" s="8">
+        <v>1252</v>
+      </c>
+      <c r="E37" s="17">
+        <f>E36+D37</f>
+        <v>1652</v>
+      </c>
+      <c r="F37" s="17"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="4">
+        <v>179</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="5">
+        <v>43872</v>
+      </c>
+      <c r="D38" s="8">
+        <v>1252</v>
+      </c>
+      <c r="E38" s="17">
+        <f>E37-D38</f>
+        <v>400</v>
+      </c>
+      <c r="G38" s="21">
+        <f>D35-G36</f>
+        <v>400</v>
+      </c>
+      <c r="H38" s="23">
+        <f>D38-G38</f>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="4">
+        <v>182</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="5">
+        <v>43893</v>
+      </c>
+      <c r="D39" s="8">
+        <v>1500</v>
+      </c>
+      <c r="E39" s="17">
+        <f>E38+D39</f>
+        <v>1900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
